--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-architecture-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-architecture-medium.xlsx
@@ -460,19 +460,19 @@
         <v>Trong Super Loop, MCU phải liên tục chạy vòng lặp để kiểm tra xem nút có nhấn không, cảm biến có dữ liệu không (Polling), giữ MCU hoạt động ở tần số cao gây hao pin. Event-driven sử dụng ngắt cạnh (Edge Interrupts) cho phép MCU tắt xung nhịp (Sleep) và chỉ hoạt động khi có xung tín hiệu kích hoạt.</v>
       </c>
       <c r="F2" t="str">
+        <v>Vì Event-Driven tự động sửa các lỗi phần cứng trên bảng mạch khi có chập điện — tự động sửa lỗi phần cứng</v>
+      </c>
+      <c r="G2" t="str">
         <v>Vì Polling liên tục quét ngoại vi làm tiêu tốn năng lượng vô ích; Event-Driven cho phép MCU ngủ sâu (Deep Sleep) và chỉ thức dậy xử lý khi có ngắt sự kiện — tiết kiệm điện năng nhờ chế độ ngủ</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
+        <v>Vì Polling làm tăng kích thước file nhị phân sau khi biên dịch lên gấp 10 lần — tăng dung lượng tệp nạp</v>
+      </c>
+      <c r="I2" t="str">
         <v>Vì Polling chỉ chạy được trên các dòng vi điều khiển ARM Cortex-M4 — giới hạn dòng chip Polling</v>
       </c>
-      <c r="H2" t="str">
-        <v>Vì Event-Driven tự động sửa các lỗi phần cứng trên bảng mạch khi có chập điện — tự động sửa lỗi phần cứng</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Vì Polling làm tăng kích thước file nhị phân sau khi biên dịch lên gấp 10 lần — tăng dung lượng tệp nạp</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -495,10 +495,10 @@
         <v>Để đảm bảo firmware ứng dụng đã được nạp hoàn chỉnh, không bị lỗi truyền dẫn hoặc lỗi hỏng bộ nhớ Flash có thể làm sập chip khi jump — kiểm tra tính toàn vẹn của firmware</v>
       </c>
       <c r="G3" t="str">
+        <v>Để tự động tăng tốc độ xử lý xung nhịp của vi điều khiển lên mức tối đa — tăng tốc độ xung nhịp chip</v>
+      </c>
+      <c r="H3" t="str">
         <v>Để giải nén kích thước file binary ứng dụng từ dạng zip sang dạng hex trên Flash — giải nén tệp tin</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Để tự động tăng tốc độ xử lý xung nhịp của vi điều khiển lên mức tối đa — tăng tốc độ xung nhịp chip</v>
       </c>
       <c r="I3" t="str">
         <v>Để mã hóa bảo mật chống hacker có thể đọc trộm mã nguồn code từ bên ngoài — bảo mật chống đọc trộm</v>
@@ -524,19 +524,19 @@
         <v>Đối với FSM nhỏ, switch-case là đủ tốt. Tuy nhiên, khi FSM có hàng chục trạng thái và điều kiện chuyển phức tạp, switch-case sẽ trở thành thảm họa khó đọc. Sử dụng mảng cấu trúc (struct) chứa: trạng thái hiện tại, sự kiện kích hoạt, trạng thái tiếp theo và con trỏ hàm xử lý (State Transition Table) giúp code sạch sẽ, dễ mở rộng.</v>
       </c>
       <c r="F4" t="str">
-        <v>Sử dụng bảng con trỏ hàm (State Transition Table / Function Pointers) trỏ tới các hàm xử lý trạng thái tương ứng — con trỏ hàm xử lý trạng thái</v>
+        <v>Sử dụng các câu lệnh nhảy không điều kiện `goto` để di chuyển tự do giữa các trạng thái — câu lệnh goto tự do rủi ro</v>
       </c>
       <c r="G4" t="str">
         <v>Viết một câu lệnh switch-case khổng lồ chứa hàng nghìn dòng code lồng nhau — switch-case khổng lồ khó đọc</v>
       </c>
       <c r="H4" t="str">
-        <v>Sử dụng các câu lệnh nhảy không điều kiện `goto` để di chuyển tự do giữa các trạng thái — câu lệnh goto tự do rủi ro</v>
+        <v>Sử dụng bảng con trỏ hàm (State Transition Table / Function Pointers) trỏ tới các hàm xử lý trạng thái tương ứng — con trỏ hàm xử lý trạng thái</v>
       </c>
       <c r="I4" t="str">
         <v>Khai báo tất cả các trạng thái thành các biến toàn cục kiểu số thực float — sử dụng biến float</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>HAL cung cấp API cho chip (như ADC, SPI, GPIO). BSP được xây dựng trên HAL, cung cấp API cho thiết bị cụ thể gắn trên board (ví dụ: Board STM32 Discovery có cảm biến gia tốc LIS3DSH, BSP cung cấp các hàm như `BSP_ACCELERO_Init()`, giúp ẩn đi việc giao tiếp SPI phức tạp cấu hình cho chip gia tốc đó).</v>
       </c>
       <c r="F5" t="str">
+        <v>HAL chỉ dùng cho lập trình nhúng 8-bit; còn BSP chỉ dùng cho lập trình nhúng 32-bit — phân loại theo bit chip</v>
+      </c>
+      <c r="G5" t="str">
         <v>HAL trừu tượng hóa vi điều khiển (MCU peripherals); BSP trừu tượng hóa toàn bộ bo mạch cụ thể bao gồm cả các linh kiện ngoại vi hàn trên bo mạch đó — trừu tượng hóa MCU vs trừu tượng hóa toàn bo mạch</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>HAL viết bằng ngôn ngữ Assembly; còn BSP viết bằng ngôn ngữ C — ngôn ngữ lập trình viết lớp</v>
-      </c>
-      <c r="H5" t="str">
-        <v>HAL chỉ dùng cho lập trình nhúng 8-bit; còn BSP chỉ dùng cho lập trình nhúng 32-bit — phân loại theo bit chip</v>
       </c>
       <c r="I5" t="str">
         <v>HAL bắt buộc phải mua bản quyền thương mại; còn BSP hoàn toàn miễn phí cho mọi người dùng — chi phí bản quyền</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -588,10 +588,10 @@
         <v>Lệnh feed watchdog (ví dụ `HAL_IWDG_Refresh()`) chỉ nên đặt ở duy nhất một vị trí an toàn (thường là cuối Super Loop sau khi tất cả các task đã hoàn thành bình thường). Nếu đặt rải rác hoặc đặt trong hàm ngắt timer, watchdog vẫn được feed đều đặn ngay cả khi chương trình chính đã bị treo cứng, vô hiệu hóa chức năng bảo vệ của WDT.</v>
       </c>
       <c r="F6" t="str">
+        <v>Vì feed watchdog nhiều nơi sẽ làm sụt áp nguồn điện của vi điều khiển ngay lập tức — sụt áp nguồn điện chip</v>
+      </c>
+      <c r="G6" t="str">
         <v>Vì nếu một đoạn code bị treo ở vòng lặp vô hạn nhưng trong vòng lặp đó vẫn có lệnh feed watchdog, hệ thống sẽ không bao giờ được reset mặc dù đã bị treo — feed watchdog trong vòng lặp treo làm mất tác dụng WDT</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Vì feed watchdog nhiều nơi sẽ làm sụt áp nguồn điện của vi điều khiển ngay lập tức — sụt áp nguồn điện chip</v>
       </c>
       <c r="H6" t="str">
         <v>Vì WDT chỉ cho phép gọi lệnh feed đúng 1 lần duy nhất trong suốt vòng đời của chip — giới hạn số lần gọi</v>
@@ -600,7 +600,7 @@
         <v>Vì nó làm cho vi điều khiển hoạt động nóng hơn gấp đôi so với bình thường — tăng sinh nhiệt phần cứng</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>FOTA an toàn đòi hỏi cơ chế Dual-bank (hoặc phân vùng Application Active và Application Download). Khi tải OTA, firmware mới được ghi vào Bank 1. Khi tải xong và validate CRC thành công, Bootloader mới đổi cờ khởi động sang Bank 1. Nếu đang tải mà mất điện, hệ thống vẫn khởi động an toàn từ Bank 0 cũ, tránh rủi ro biến thiết bị thành "cục gạch" (bricking).</v>
       </c>
       <c r="F7" t="str">
-        <v>Phải có cơ chế phân vùng bộ nhớ Dual-bank Flash (gồm Bank 0 chứa Application đang chạy, Bank 1 chứa ứng dụng mới đang tải về) để rollback nếu cập nhật thất bại — phân vùng Dual-bank Flash</v>
+        <v>Phải hỗ trợ kết nối trực tiếp với thẻ nhớ ngoài SD chạy song song — thẻ nhớ ngoài SD</v>
       </c>
       <c r="G7" t="str">
         <v>Phải có dung lượng Flash tối thiểu từ 16GB trở lên giống như trên điện thoại di động di động — yêu cầu dung lượng Flash lớn</v>
       </c>
       <c r="H7" t="str">
-        <v>Phải hỗ trợ kết nối trực tiếp với thẻ nhớ ngoài SD chạy song song — thẻ nhớ ngoài SD</v>
+        <v>Phải có cơ chế phân vùng bộ nhớ Dual-bank Flash (gồm Bank 0 chứa Application đang chạy, Bank 1 chứa ứng dụng mới đang tải về) để rollback nếu cập nhật thất bại — phân vùng Dual-bank Flash</v>
       </c>
       <c r="I7" t="str">
         <v>Chỉ được phép sử dụng bộ nhớ RAM để lưu trữ firmware mới chứ không nạp vào Flash — nạp vào RAM</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Callback đăng ký con trỏ hàm. Ví dụ: khi nhận xong 1 byte UART, HAL phát sinh ngắt và tự động gọi hàm callback `HAL_UART_RxCpltCallback()`. Lập trình viên chỉ cần viết logic xử lý byte đó trong hàm callback ở lớp Application mà không cần sửa code Driver của HAL.</v>
       </c>
       <c r="F8" t="str">
-        <v>Cho phép lớp phần cứng (driver/HAL) kích hoạt ngược lại một hàm xử lý được định nghĩa ở lớp ứng dụng (application) khi có sự kiện ngắt xảy ra — gọi ngược hàm xử lý lớp ứng dụng</v>
+        <v>Mã hóa toàn bộ các bản tin dữ liệu truyền đi qua giao thức UART sang mã Hex — mã hóa dữ liệu UART</v>
       </c>
       <c r="G8" t="str">
         <v>Tự động xóa các biến toàn cục không sử dụng ra khỏi bộ nhớ của vi điều khiển — tự động xóa biến rác</v>
       </c>
       <c r="H8" t="str">
-        <v>Mã hóa toàn bộ các bản tin dữ liệu truyền đi qua giao thức UART sang mã Hex — mã hóa dữ liệu UART</v>
+        <v>Yêu cầu lập trình viên phải chạy chương trình mô phỏng trên phần mềm trước khi nạp vào chip — mô phỏng bắt buộc</v>
       </c>
       <c r="I8" t="str">
-        <v>Yêu cầu lập trình viên phải chạy chương trình mô phỏng trên phần mềm trước khi nạp vào chip — mô phỏng bắt buộc</v>
+        <v>Cho phép lớp phần cứng (driver/HAL) kích hoạt ngược lại một hàm xử lý được định nghĩa ở lớp ứng dụng (application) khi có sự kiện ngắt xảy ra — gọi ngược hàm xử lý lớp ứng dụng</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Trình biên dịch khi tối ưu hóa (Optimization levels -O2, -O3) thấy biến toàn cục không bị sửa đổi trong vòng lặp `while(1)` chính sẽ cất nó vào thanh ghi CPU để đọc nhanh. Nhưng ISR có thể sửa biến này dưới phần cứng. Nếu thiếu `volatile`, vòng lặp chính sẽ đọc giá trị cũ trong thanh ghi mãi mãi, gây lỗi logic hệ thống.</v>
       </c>
       <c r="F9" t="str">
+        <v>Để hệ thống tự động khóa tất cả các ngắt chéo khi biến này đang được ghi dữ liệu — tự động khóa ngắt chéo</v>
+      </c>
+      <c r="G9" t="str">
         <v>Để báo cho trình biên dịch (Compiler) không được tối ưu hóa biến này vào thanh ghi, bắt buộc phải đọc trực tiếp từ bộ nhớ RAM vì giá trị có thể thay đổi bất ngờ ngoài luồng chính — ngăn chặn tối ưu hóa trình biên dịch</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Để tăng tốc độ đọc ghi của biến này trên bộ nhớ RAM lên nhanh gấp 10 lần — tăng tốc độ đọc ghi biến</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Để hệ thống tự động khóa tất cả các ngắt chéo khi biến này đang được ghi dữ liệu — tự động khóa ngắt chéo</v>
       </c>
       <c r="I9" t="str">
         <v>Vì nếu không có volatile, vi điều khiển sẽ tự động reset lại chip khi biến đó nhận giá trị số âm — reset khi giá trị âm</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -719,10 +719,10 @@
         <v>Vì malloc tốn tài nguyên quản lý của heap, có rủi ro rò rỉ bộ nhớ (memory leak) và gây phân mảnh RAM dẫn đến việc không thể cấp phát được sau một thời gian chạy — rủi ro phân mảnh và cạn kiệt RAM</v>
       </c>
       <c r="G10" t="str">
+        <v>Vì hàm free() tự động xóa bỏ toàn bộ mã nguồn chương trình lưu trong Flash của chip — tự động xóa code</v>
+      </c>
+      <c r="H10" t="str">
         <v>Vì malloc chỉ hoạt động được trên các vi điều khiển hỗ trợ hệ điều hành RTOS — giới hạn hệ điều hành</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Vì hàm free() tự động xóa bỏ toàn bộ mã nguồn chương trình lưu trong Flash của chip — tự động xóa code</v>
       </c>
       <c r="I10" t="str">
         <v>Vì cấp phát động bắt buộc vi điều khiển phải chạy ở tần số xung nhịp tối thiểu là 100MHz — giới hạn tần số chip</v>
@@ -748,19 +748,19 @@
         <v>Trong Moore Machine, ngõ ra (Output) thay đổi đồng bộ với sự chuyển đổi trạng thái (State). Trong Mealy Machine, ngõ ra có thể thay đổi ngay lập tức khi tín hiệu ngõ vào (Input) thay đổi bất kể trạng thái hiện tại, giúp phản hồi nhanh hơn nhưng dễ bị nhiễu tín hiệu đầu vào.</v>
       </c>
       <c r="F11" t="str">
+        <v>Moore bắt buộc phải có tối thiểu 4 trạng thái; còn Mealy hỗ trợ vô hạn trạng thái — giới hạn số lượng trạng thái</v>
+      </c>
+      <c r="G11" t="str">
         <v>Moore: Đầu ra chỉ phụ thuộc vào trạng thái hiện tại; Mealy: Đầu ra phụ thuộc vào cả trạng thái hiện tại và tín hiệu đầu vào — đầu ra phụ thuộc trạng thái vs phụ thuộc trạng thái &amp; đầu vào</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
+        <v>Moore chạy nhanh hơn Mealy do cấu trúc mạch logic đơn giản hơn rất nhiều — so sánh hiệu năng tốc độ</v>
+      </c>
+      <c r="I11" t="str">
         <v>Moore chỉ dùng cho thiết kế phần cứng; còn Mealy chỉ dùng cho thiết kế phần mềm — phân loại đối tượng thiết kế</v>
       </c>
-      <c r="H11" t="str">
-        <v>Moore bắt buộc phải có tối thiểu 4 trạng thái; còn Mealy hỗ trợ vô hạn trạng thái — giới hạn số lượng trạng thái</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Moore chạy nhanh hơn Mealy do cấu trúc mạch logic đơn giản hơn rất nhiều — so sánh hiệu năng tốc độ</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
